--- a/results/682_z08/2_canaliculi/682_z08_canaliculi_results.xlsx
+++ b/results/682_z08/2_canaliculi/682_z08_canaliculi_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +682,441 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>275.4257</v>
+      </c>
+      <c r="D12" t="n">
+        <v>240.4299</v>
+      </c>
+      <c r="E12" t="n">
+        <v>89.7432</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>10379.625</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9533.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2334.0449</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24427.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24429.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5136.867</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>px^2</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.9949</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>unitless</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03800643</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.03766433</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.00650669</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.04004776</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.04065321</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.008509630000000001</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>normalised</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.6845</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>per 100 px</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>317.125</v>
+      </c>
+      <c r="D20" t="n">
+        <v>284</v>
+      </c>
+      <c r="E20" t="n">
+        <v>135.0423</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>673.25</v>
+      </c>
+      <c r="D21" t="n">
+        <v>584.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>354.146</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>445.9204</v>
+      </c>
+      <c r="D22" t="n">
+        <v>397.3686</v>
+      </c>
+      <c r="E22" t="n">
+        <v>141.6018</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1103.9582</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1012.9884</v>
+      </c>
+      <c r="E23" t="n">
+        <v>365.4032</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5.0356</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>4.4641</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>network v2</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5.1547</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
         <v>8</v>
       </c>
     </row>
@@ -696,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,6 +1353,63 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>field_length_density_w_per_px</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.03869506</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>field_density_without_flagged_per_px</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.03502703</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>field_density_in_roi_per_px</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
         </is>
       </c>
     </row>
@@ -932,7 +1424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,6 +1468,81 @@
           <t>mean_edge_length_px</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>perimeter_px</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ring_area_r30_px2</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ring_area_r60_px2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r30</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>in_frame_fraction_r60</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ring_density_r30</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>ring_density_r60</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>roots_per_100px_perimeter</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r30_px</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ring_attached_length_r60_px</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r30_px</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring_length_w_r60_px</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r10</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r20</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sholl_crossings_r30</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1002,6 +1569,51 @@
       <c r="H2" t="n">
         <v>22.8907</v>
       </c>
+      <c r="I2" t="n">
+        <v>769.5412</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14367</v>
+      </c>
+      <c r="K2" t="n">
+        <v>29344</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6579</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.6229</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.02561425</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.03254498</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.2995</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>254</v>
+      </c>
+      <c r="R2" t="n">
+        <v>366</v>
+      </c>
+      <c r="S2" t="n">
+        <v>398.7056</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1026.4113</v>
+      </c>
+      <c r="U2" t="n">
+        <v>12</v>
+      </c>
+      <c r="V2" t="n">
+        <v>11</v>
+      </c>
+      <c r="W2" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1028,6 +1640,51 @@
       <c r="H3" t="n">
         <v>23.3235</v>
       </c>
+      <c r="I3" t="n">
+        <v>234.8944</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9374</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20769</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.9593</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.03968423</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.04776349</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.2572</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>303</v>
+      </c>
+      <c r="R3" t="n">
+        <v>656</v>
+      </c>
+      <c r="S3" t="n">
+        <v>421.7767</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1099.5361</v>
+      </c>
+      <c r="U3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V3" t="n">
+        <v>14</v>
+      </c>
+      <c r="W3" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1054,6 +1711,51 @@
       <c r="H4" t="n">
         <v>31.1734</v>
       </c>
+      <c r="I4" t="n">
+        <v>313.9483</v>
+      </c>
+      <c r="J4" t="n">
+        <v>11274</v>
+      </c>
+      <c r="K4" t="n">
+        <v>26474</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.03308497</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.03731963</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4.1408</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>312</v>
+      </c>
+      <c r="R4" t="n">
+        <v>591</v>
+      </c>
+      <c r="S4" t="n">
+        <v>420.3747</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1118.0874</v>
+      </c>
+      <c r="U4" t="n">
+        <v>13</v>
+      </c>
+      <c r="V4" t="n">
+        <v>12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1782,51 @@
       <c r="H5" t="n">
         <v>23.3567</v>
       </c>
+      <c r="I5" t="n">
+        <v>456.9605</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14983</v>
+      </c>
+      <c r="K5" t="n">
+        <v>32605</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.04351598</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.04956295</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.9391</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>622</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1480</v>
+      </c>
+      <c r="S5" t="n">
+        <v>726.1858999999999</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1818.1778</v>
+      </c>
+      <c r="U5" t="n">
+        <v>21</v>
+      </c>
+      <c r="V5" t="n">
+        <v>23</v>
+      </c>
+      <c r="W5" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1106,6 +1853,51 @@
       <c r="H6" t="n">
         <v>23.7572</v>
       </c>
+      <c r="I6" t="n">
+        <v>233.2376</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9202</v>
+      </c>
+      <c r="K6" t="n">
+        <v>19621</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.03564443</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03480964</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>227</v>
+      </c>
+      <c r="R6" t="n">
+        <v>393</v>
+      </c>
+      <c r="S6" t="n">
+        <v>374.3625</v>
+      </c>
+      <c r="T6" t="n">
+        <v>776.7666</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>12</v>
+      </c>
+      <c r="W6" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1132,6 +1924,51 @@
       <c r="H7" t="n">
         <v>16.7862</v>
       </c>
+      <c r="I7" t="n">
+        <v>166.1249</v>
+      </c>
+      <c r="J7" t="n">
+        <v>7387</v>
+      </c>
+      <c r="K7" t="n">
+        <v>17424</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.04616218</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.04820937</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.0098</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>265</v>
+      </c>
+      <c r="R7" t="n">
+        <v>578</v>
+      </c>
+      <c r="S7" t="n">
+        <v>373.5219</v>
+      </c>
+      <c r="T7" t="n">
+        <v>926.4407</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>11</v>
+      </c>
+      <c r="W7" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1158,6 +1995,51 @@
       <c r="H8" t="n">
         <v>36.765</v>
       </c>
+      <c r="I8" t="n">
+        <v>122.6041</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3917</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10590</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6212</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5802</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03829461</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.03918791</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.4469</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>88</v>
+      </c>
+      <c r="R8" t="n">
+        <v>194</v>
+      </c>
+      <c r="S8" t="n">
+        <v>170.9239</v>
+      </c>
+      <c r="T8" t="n">
+        <v>478.6295</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1183,6 +2065,51 @@
       </c>
       <c r="H9" t="n">
         <v>28.1298</v>
+      </c>
+      <c r="I9" t="n">
+        <v>329.5219</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12020</v>
+      </c>
+      <c r="K9" t="n">
+        <v>29668</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0437604</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.04398679</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.9451</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>375</v>
+      </c>
+      <c r="R9" t="n">
+        <v>815</v>
+      </c>
+      <c r="S9" t="n">
+        <v>589.9016</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1448.7443</v>
+      </c>
+      <c r="U9" t="n">
+        <v>13</v>
+      </c>
+      <c r="V9" t="n">
+        <v>19</v>
+      </c>
+      <c r="W9" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -1210,6 +2137,51 @@
       <c r="H10" t="n">
         <v>26.3879</v>
       </c>
+      <c r="I10" t="n">
+        <v>222.7523</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9104</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23858</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.03547891</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.03177131</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.1425</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>221</v>
+      </c>
+      <c r="R10" t="n">
+        <v>447</v>
+      </c>
+      <c r="S10" t="n">
+        <v>368.6468</v>
+      </c>
+      <c r="T10" t="n">
+        <v>884.46</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>13</v>
+      </c>
+      <c r="W10" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1235,6 +2207,51 @@
       </c>
       <c r="H11" t="n">
         <v>30.7393</v>
+      </c>
+      <c r="I11" t="n">
+        <v>245.9655</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9693</v>
+      </c>
+      <c r="K11" t="n">
+        <v>25001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.02672031</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.02695892</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.4394</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>212</v>
+      </c>
+      <c r="R11" t="n">
+        <v>426</v>
+      </c>
+      <c r="S11" t="n">
+        <v>292.5929</v>
+      </c>
+      <c r="T11" t="n">
+        <v>759.4529</v>
+      </c>
+      <c r="U11" t="n">
+        <v>8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>10</v>
+      </c>
+      <c r="W11" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
